--- a/03_今年度用/測定_20260818/等価コンクリート_減衰解析.xlsx
+++ b/03_今年度用/測定_20260818/等価コンクリート_減衰解析.xlsx
@@ -319,7 +319,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>相対CPSと理論減衰 A=A0·EXP(-x/77)（x [cm]）</a:t>
+              <a:t>相対CPSと理論減衰 A=A0·EXP(-x/λ_c)（x [cm]）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -331,7 +331,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>理論 A=A0·EXP(-x/77)</v>
+            <v>理論 A=A0·EXP(-x/λ_c)</v>
           </tx>
           <spPr>
             <a:ln w="25000">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>77</v>
+        <v>39.17953109099486</v>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>lambda_cm / 100 (=0.77 m)</t>
+          <t>lambda_cm / 100 (=λ_c from detailed MFP)</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>理論セル例: =パラメータ!$B$5*EXP(-G5/パラメータ!$B$6)  （G=t_eq[cm], B6=lambda=77cm）</t>
+          <t>理論セル例: =パラメータ!$B$5*EXP(-G5/パラメータ!$B$6)  （G=t_eq[cm], B6=lambda=λ_c cm）</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>土はロームのみ（220 cm &lt; 4 m）</t>
+          <t>土はロームのみ（220 cm &lt; 3.5 m）</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>ローム4 m + 常総2.7 m（Book5の117.25は桁誤り）</t>
+          <t>ローム3.5 m + 常総2.0 m + 下総1.2 m（Book5の117.25は桁誤り）</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>EXP(-150/77)</t>
+          <t>EXP(-150/λ_c)</t>
         </is>
       </c>
       <c r="B13" s="26">
@@ -1942,14 +1942,14 @@
     </row>
     <row r="6">
       <c r="A6" s="19" t="n">
-        <v>10.576348</v>
+        <v>10.929043</v>
       </c>
       <c r="B6" s="26">
         <f>パラメータ!$B$5*EXP(-A6/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C6" s="29" t="n">
-        <v>0.8716605864456096</v>
+        <v>0.75657940575914</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>0.4781264150232363</v>
       </c>
       <c r="J6" s="31" t="n">
-        <v>0.2557291599131006</v>
+        <v>0.06856515497031862</v>
       </c>
       <c r="K6" s="32" t="inlineStr">
         <is>
@@ -1982,14 +1982,14 @@
     </row>
     <row r="7">
       <c r="A7" s="19" t="n">
-        <v>21.152696</v>
+        <v>21.858087</v>
       </c>
       <c r="B7" s="26">
         <f>パラメータ!$B$5*EXP(-A7/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C7" s="29" t="n">
-        <v>0.759792177962704</v>
+        <v>0.5724123972188533</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>0.1233735641158972</v>
       </c>
       <c r="J7" s="31" t="n">
-        <v>0.1425514990025999</v>
+        <v>0.02174155787480851</v>
       </c>
       <c r="K7" s="32" t="inlineStr">
         <is>
@@ -2022,14 +2022,14 @@
     </row>
     <row r="8">
       <c r="A8" s="19" t="n">
-        <v>31.729043</v>
+        <v>32.78713</v>
       </c>
       <c r="B8" s="26">
         <f>パラメータ!$B$5*EXP(-A8/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C8" s="29" t="n">
-        <v>0.6622808954197575</v>
+        <v>0.4330754313370048</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>0.2185234516795397</v>
       </c>
       <c r="J8" s="31" t="n">
-        <v>0.08575684142290207</v>
+        <v>0.008008301167854356</v>
       </c>
       <c r="K8" s="32" t="inlineStr">
         <is>
@@ -2062,14 +2062,14 @@
     </row>
     <row r="9">
       <c r="A9" s="19" t="n">
-        <v>42.305391</v>
+        <v>43.716174</v>
       </c>
       <c r="B9" s="26">
         <f>パラメータ!$B$5*EXP(-A9/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C9" s="29" t="n">
-        <v>0.5772841536933092</v>
+        <v>0.3276559524898343</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>508.4782608695652</v>
+        <v>525.4347826086957</v>
       </c>
       <c r="H9" s="30">
         <f>測定点!F9</f>
@@ -2087,7 +2087,7 @@
         <v>0.07604057210988405</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>0.001355460842202139</v>
+        <v>1.498641870984568e-06</v>
       </c>
       <c r="K9" s="32" t="inlineStr">
         <is>
@@ -2102,554 +2102,554 @@
     </row>
     <row r="10">
       <c r="A10" s="19" t="n">
-        <v>52.881739</v>
+        <v>54.645217</v>
       </c>
       <c r="B10" s="26">
         <f>パラメータ!$B$5*EXP(-A10/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C10" s="29" t="n">
-        <v>0.5031958439540674</v>
+        <v>0.2478977458282038</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n">
-        <v>63.458087</v>
+        <v>65.57426100000001</v>
       </c>
       <c r="B11" s="26">
         <f>パラメータ!$B$5*EXP(-A11/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C11" s="29" t="n">
-        <v>0.4386159844379958</v>
+        <v>0.1875543292277328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n">
-        <v>74.034435</v>
+        <v>76.503304</v>
       </c>
       <c r="B12" s="26">
         <f>パラメータ!$B$5*EXP(-A12/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C12" s="29" t="n">
-        <v>0.3823242662196418</v>
+        <v>0.1418997429546721</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>84.610783</v>
+        <v>87.432348</v>
       </c>
       <c r="B13" s="26">
         <f>パラメータ!$B$5*EXP(-A13/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C13" s="29" t="n">
-        <v>0.3332569941054003</v>
+        <v>0.1073584232020205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="n">
-        <v>95.18713</v>
+        <v>98.361391</v>
       </c>
       <c r="B14" s="26">
         <f>パラメータ!$B$5*EXP(-A14/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C14" s="29" t="n">
-        <v>0.2904869869190142</v>
+        <v>0.08122517202942296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n">
-        <v>105.763478</v>
+        <v>109.290435</v>
       </c>
       <c r="B15" s="26">
         <f>パラメータ!$B$5*EXP(-A15/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C15" s="29" t="n">
-        <v>0.2532060573726461</v>
+        <v>0.06145329238670474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="n">
-        <v>116.339826</v>
+        <v>120.219478</v>
       </c>
       <c r="B16" s="26">
         <f>パラメータ!$B$5*EXP(-A16/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.2207097404610214</v>
+        <v>0.04649429543587575</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="n">
-        <v>126.916174</v>
+        <v>131.148522</v>
       </c>
       <c r="B17" s="26">
         <f>パラメータ!$B$5*EXP(-A17/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C17" s="29" t="n">
-        <v>0.1923839818045122</v>
+        <v>0.03517662641206477</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>137.492522</v>
+        <v>142.077565</v>
       </c>
       <c r="B18" s="26">
         <f>パラメータ!$B$5*EXP(-A18/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C18" s="29" t="n">
-        <v>0.1676935344024625</v>
+        <v>0.02661391110745121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>148.06887</v>
+        <v>153.006609</v>
       </c>
       <c r="B19" s="26">
         <f>パラメータ!$B$5*EXP(-A19/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C19" s="29" t="n">
-        <v>0.1461718445403875</v>
+        <v>0.02013553705060202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>158.645217</v>
+        <v>163.935652</v>
       </c>
       <c r="B20" s="26">
         <f>パラメータ!$B$5*EXP(-A20/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C20" s="29" t="n">
-        <v>0.1274122357339107</v>
+        <v>0.01523413265638561</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>169.221565</v>
+        <v>174.864696</v>
       </c>
       <c r="B21" s="26">
         <f>パラメータ!$B$5*EXP(-A21/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C21" s="29" t="n">
-        <v>0.1110602241201668</v>
+        <v>0.01152583103242414</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>179.797913</v>
+        <v>185.793739</v>
       </c>
       <c r="B22" s="26">
         <f>パラメータ!$B$5*EXP(-A22/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C22" s="29" t="n">
-        <v>0.09680682008736539</v>
+        <v>0.008720206393391716</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="n">
-        <v>190.374261</v>
+        <v>196.722783</v>
       </c>
       <c r="B23" s="26">
         <f>パラメータ!$B$5*EXP(-A23/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C23" s="29" t="n">
-        <v>0.08438268956928754</v>
+        <v>0.006597528571209354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="n">
-        <v>200.950609</v>
+        <v>207.651826</v>
       </c>
       <c r="B24" s="26">
         <f>パラメータ!$B$5*EXP(-A24/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C24" s="29" t="n">
-        <v>0.07355306467582304</v>
+        <v>0.004991554245884519</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="n">
-        <v>211.526957</v>
+        <v>218.58087</v>
       </c>
       <c r="B25" s="26">
         <f>パラメータ!$B$5*EXP(-A25/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C25" s="29" t="n">
-        <v>0.06411330749019976</v>
+        <v>0.003776507145165823</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="n">
-        <v>222.103304</v>
+        <v>229.509913</v>
       </c>
       <c r="B26" s="26">
         <f>パラメータ!$B$5*EXP(-A26/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C26" s="29" t="n">
-        <v>0.05588504320587522</v>
+        <v>0.002857227531734703</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="n">
-        <v>232.679652</v>
+        <v>240.438957</v>
       </c>
       <c r="B27" s="26">
         <f>パラメータ!$B$5*EXP(-A27/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C27" s="29" t="n">
-        <v>0.04871278953437142</v>
+        <v>0.002161719508078497</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>243.256</v>
+        <v>251.368</v>
       </c>
       <c r="B28" s="26">
         <f>パラメータ!$B$5*EXP(-A28/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C28" s="29" t="n">
-        <v>0.04246101869293173</v>
+        <v>0.001635512460839969</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>253.832348</v>
+        <v>262.297043</v>
       </c>
       <c r="B29" s="26">
         <f>パラメータ!$B$5*EXP(-A29/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C29" s="29" t="n">
-        <v>0.03701159645495886</v>
+        <v>0.001237395045733973</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>264.408696</v>
+        <v>273.226087</v>
       </c>
       <c r="B30" s="26">
         <f>パラメータ!$B$5*EXP(-A30/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C30" s="29" t="n">
-        <v>0.03226154987121769</v>
+        <v>0.0009361876083907126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="n">
-        <v>274.985043</v>
+        <v>284.15513</v>
       </c>
       <c r="B31" s="26">
         <f>パラメータ!$B$5*EXP(-A31/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C31" s="29" t="n">
-        <v>0.02812112148038988</v>
+        <v>0.0007083002644353148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="n">
-        <v>285.561391</v>
+        <v>295.084174</v>
       </c>
       <c r="B32" s="26">
         <f>パラメータ!$B$5*EXP(-A32/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C32" s="29" t="n">
-        <v>0.02451207324110488</v>
+        <v>0.0005358853931655129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="n">
-        <v>296.137739</v>
+        <v>306.013217</v>
       </c>
       <c r="B33" s="26">
         <f>パラメータ!$B$5*EXP(-A33/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C33" s="29" t="n">
-        <v>0.02136620813633922</v>
+        <v>0.0004054398523161667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="n">
-        <v>306.714087</v>
+        <v>316.942261</v>
       </c>
       <c r="B34" s="26">
         <f>パラメータ!$B$5*EXP(-A34/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C34" s="29" t="n">
-        <v>0.01862408151424039</v>
+        <v>0.0003067474425364393</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="n">
-        <v>317.290435</v>
+        <v>327.871304</v>
       </c>
       <c r="B35" s="26">
         <f>パラメータ!$B$5*EXP(-A35/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C35" s="29" t="n">
-        <v>0.01623387781471362</v>
+        <v>0.0002320787977923546</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="n">
-        <v>327.866783</v>
+        <v>338.800348</v>
       </c>
       <c r="B36" s="26">
         <f>パラメータ!$B$5*EXP(-A36/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C36" s="29" t="n">
-        <v>0.01415043145625964</v>
+        <v>0.0001755860389230352</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="n">
-        <v>338.44313</v>
+        <v>349.729391</v>
       </c>
       <c r="B37" s="26">
         <f>パラメータ!$B$5*EXP(-A37/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C37" s="29" t="n">
-        <v>0.01233437338162168</v>
+        <v>0.0001328447809879914</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="n">
-        <v>349.019478</v>
+        <v>360.658435</v>
       </c>
       <c r="B38" s="26">
         <f>パラメータ!$B$5*EXP(-A38/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C38" s="29" t="n">
-        <v>0.01075138713526348</v>
+        <v>0.0001005076254580976</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="n">
-        <v>359.595826</v>
+        <v>371.587478</v>
       </c>
       <c r="B39" s="26">
         <f>パラメータ!$B$5*EXP(-A39/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C39" s="29" t="n">
-        <v>0.009371560415427534</v>
+        <v>7.604199954334975e-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="n">
-        <v>370.172174</v>
+        <v>382.516522</v>
       </c>
       <c r="B40" s="26">
         <f>パラメータ!$B$5*EXP(-A40/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C40" s="29" t="n">
-        <v>0.008168819847622031</v>
+        <v>5.753181082724422e-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="n">
-        <v>380.748522</v>
+        <v>393.445565</v>
       </c>
       <c r="B41" s="26">
         <f>パラメータ!$B$5*EXP(-A41/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C41" s="29" t="n">
-        <v>0.007120438298946749</v>
+        <v>4.352738324792374e-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="n">
-        <v>391.32487</v>
+        <v>404.374609</v>
       </c>
       <c r="B42" s="26">
         <f>パラメータ!$B$5*EXP(-A42/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C42" s="29" t="n">
-        <v>0.006206605423409702</v>
+        <v>3.293192175196448e-05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="n">
-        <v>401.901217</v>
+        <v>415.303652</v>
       </c>
       <c r="B43" s="26">
         <f>パラメータ!$B$5*EXP(-A43/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C43" s="29" t="n">
-        <v>0.005410053323205806</v>
+        <v>2.491561378960777e-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n">
-        <v>412.477565</v>
+        <v>426.232696</v>
       </c>
       <c r="B44" s="26">
         <f>パラメータ!$B$5*EXP(-A44/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C44" s="29" t="n">
-        <v>0.004715730252407588</v>
+        <v>1.885064027506567e-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n">
-        <v>423.053913</v>
+        <v>437.161739</v>
       </c>
       <c r="B45" s="26">
         <f>パラメータ!$B$5*EXP(-A45/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C45" s="29" t="n">
-        <v>0.004110516197332904</v>
+        <v>1.426200621748851e-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="n">
-        <v>433.630261</v>
+        <v>448.090783</v>
       </c>
       <c r="B46" s="26">
         <f>パラメータ!$B$5*EXP(-A46/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C46" s="29" t="n">
-        <v>0.003582974959161377</v>
+        <v>1.07903401889606e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="n">
-        <v>444.206609</v>
+        <v>459.019826</v>
       </c>
       <c r="B47" s="26">
         <f>パラメータ!$B$5*EXP(-A47/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C47" s="29" t="n">
-        <v>0.003123138054122539</v>
+        <v>8.163749168102784e-06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="n">
-        <v>454.782957</v>
+        <v>469.94887</v>
       </c>
       <c r="B48" s="26">
         <f>パラメータ!$B$5*EXP(-A48/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C48" s="29" t="n">
-        <v>0.002722316347807053</v>
+        <v>6.176524494369875e-06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="n">
-        <v>465.359304</v>
+        <v>480.877913</v>
       </c>
       <c r="B49" s="26">
         <f>パラメータ!$B$5*EXP(-A49/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C49" s="29" t="n">
-        <v>0.002372935864219966</v>
+        <v>4.673031231607138e-06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="n">
-        <v>475.935652</v>
+        <v>491.806957</v>
       </c>
       <c r="B50" s="26">
         <f>パラメータ!$B$5*EXP(-A50/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C50" s="29" t="n">
-        <v>0.002068394667003793</v>
+        <v>3.535519192303229e-06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="n">
-        <v>486.512</v>
+        <v>502.736</v>
       </c>
       <c r="B51" s="26">
         <f>パラメータ!$B$5*EXP(-A51/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C51" s="29" t="n">
-        <v>0.001802938108441498</v>
+        <v>2.67490100956281e-06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="n">
-        <v>497.088348</v>
+        <v>513.665043</v>
       </c>
       <c r="B52" s="26">
         <f>パラメータ!$B$5*EXP(-A52/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C52" s="29" t="n">
-        <v>0.001571550088929254</v>
+        <v>2.023775016279554e-06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="n">
-        <v>507.664696</v>
+        <v>524.5940869999999</v>
       </c>
       <c r="B53" s="26">
         <f>パラメータ!$B$5*EXP(-A53/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C53" s="29" t="n">
-        <v>0.001369858272144723</v>
+        <v>1.531146499206981e-06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="n">
-        <v>518.241043</v>
+        <v>535.52313</v>
       </c>
       <c r="B54" s="26">
         <f>パラメータ!$B$5*EXP(-A54/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C54" s="29" t="n">
-        <v>0.001194051464845039</v>
+        <v>1.158433908500202e-06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="n">
-        <v>528.817391</v>
+        <v>546.452174</v>
       </c>
       <c r="B55" s="26">
         <f>パラメータ!$B$5*EXP(-A55/パラメータ!$B$6)</f>
         <v/>
       </c>
       <c r="C55" s="29" t="n">
-        <v>0.001040807600093066</v>
+        <v>8.764472381043222e-07</v>
       </c>
     </row>
     <row r="57">
@@ -2862,7 +2862,7 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>・PNG図: figures/11_全地点_等価コンクリート.png。理論は A=A0·exp(-x/77)、xは等価コンクリート厚[cm]。</t>
+          <t>・PNG図: figures/11_全地点_等価コンクリート.png。理論は A=A0·exp(-x/λ_c)、xは等価コンクリート厚[cm]。</t>
         </is>
       </c>
     </row>
